--- a/data/trans_dic/P25A$rendimiento-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P25A$rendimiento-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, la disminución del rendimiento</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, la disminución del rendimiento (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 6,22</t>
+          <t>0,74; 6,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,11; 11,19</t>
+          <t>4,11; 11,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,29; 13,71</t>
+          <t>3,57; 15,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 16,67</t>
+          <t>2,05; 16,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,2</t>
+          <t>0,0; 9,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 7,07</t>
+          <t>1,21; 6,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,67; 8,38</t>
+          <t>2,65; 8,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 10,02</t>
+          <t>2,92; 10,84</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 8,49</t>
+          <t>2,53; 8,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,66</t>
+          <t>0,42; 3,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 7,42</t>
+          <t>1,14; 7,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,91</t>
+          <t>0,0; 7,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 11,92</t>
+          <t>2,03; 11,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 9,73</t>
+          <t>1,07; 9,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 6,99</t>
+          <t>1,91; 6,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,73</t>
+          <t>1,23; 4,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 6,33</t>
+          <t>1,82; 7,19</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,17</t>
+          <t>0,0; 5,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 6,16</t>
+          <t>1,14; 6,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 7,97</t>
+          <t>0,8; 8,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 20,88</t>
+          <t>2,32; 20,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 8,07</t>
+          <t>0,93; 8,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,38; 12,45</t>
+          <t>1,38; 12,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 6,45</t>
+          <t>1,12; 6,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 5,78</t>
+          <t>1,44; 5,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 7,4</t>
+          <t>1,96; 7,94</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 6,33</t>
+          <t>1,47; 6,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,86; 8,07</t>
+          <t>1,85; 7,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,59; 10,84</t>
+          <t>3,47; 11,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,13; 12,63</t>
+          <t>2,07; 11,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 9,98</t>
+          <t>0,84; 9,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,6; 12,14</t>
+          <t>2,59; 11,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,12; 7,0</t>
+          <t>2,13; 6,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,57</t>
+          <t>2,1; 7,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,06; 9,62</t>
+          <t>4,03; 9,66</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,88</t>
+          <t>2,06; 4,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,44; 5,24</t>
+          <t>2,54; 5,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,62; 7,42</t>
+          <t>3,39; 7,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,93; 8,42</t>
+          <t>2,77; 8,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 5,66</t>
+          <t>1,69; 5,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,86; 7,45</t>
+          <t>2,74; 7,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,66; 5,01</t>
+          <t>2,65; 5,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,84</t>
+          <t>2,56; 4,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,75; 6,54</t>
+          <t>3,51; 6,36</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, la disminución del rendimiento</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, la disminución del rendimiento (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>969; 8048</t>
+          <t>962; 8210</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7752; 21106</t>
+          <t>7757; 21139</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3884; 16208</t>
+          <t>4216; 18022</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>840; 6884</t>
+          <t>848; 6849</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 2000</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4948</t>
+          <t>0; 5123</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1975; 12072</t>
+          <t>2062; 11780</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6971; 21845</t>
+          <t>6914; 22123</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4721; 17243</t>
+          <t>5021; 18654</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4001; 15855</t>
+          <t>4733; 16603</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1036; 9100</t>
+          <t>1035; 7971</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2014; 13157</t>
+          <t>2024; 12688</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 6083</t>
+          <t>0; 5723</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2167; 11716</t>
+          <t>1992; 11670</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>915; 8403</t>
+          <t>920; 8448</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5072; 18433</t>
+          <t>5034; 18419</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4135; 16415</t>
+          <t>4269; 15846</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4032; 16676</t>
+          <t>4804; 18959</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6939</t>
+          <t>0; 7205</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1972; 10609</t>
+          <t>1967; 11268</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1018; 10647</t>
+          <t>1062; 10977</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>930; 8284</t>
+          <t>922; 8279</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>959; 8321</t>
+          <t>960; 8281</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1030; 9283</t>
+          <t>1027; 9369</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1896; 11223</t>
+          <t>1946; 11343</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3998; 15934</t>
+          <t>3960; 15339</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4006; 15403</t>
+          <t>4076; 16518</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2533; 11021</t>
+          <t>2563; 12061</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3836; 16653</t>
+          <t>3825; 16149</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6339; 19130</t>
+          <t>6126; 19683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1973; 11721</t>
+          <t>1925; 10629</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>964; 11281</t>
+          <t>949; 10592</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3153; 14706</t>
+          <t>3132; 14276</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5647; 18683</t>
+          <t>5695; 17837</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6532; 20995</t>
+          <t>6715; 22552</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12085; 28639</t>
+          <t>11981; 28742</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13128; 30466</t>
+          <t>12841; 29474</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19923; 42768</t>
+          <t>20728; 43390</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21916; 44924</t>
+          <t>20534; 43484</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7348; 21121</t>
+          <t>6940; 21806</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6864; 21879</t>
+          <t>6521; 20973</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9618; 25014</t>
+          <t>9209; 24915</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23317; 43831</t>
+          <t>23224; 43983</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>30754; 58175</t>
+          <t>30736; 57019</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35259; 61580</t>
+          <t>33082; 59840</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25A$rendimiento-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P25A$rendimiento-Habitat-trans_dic.xlsx
@@ -678,22 +678,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,34</t>
+          <t>0,75; 6,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,11; 11,2</t>
+          <t>4,08; 11,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,57; 15,25</t>
+          <t>3,5; 14,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,05; 16,58</t>
+          <t>2,1; 17,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -703,22 +703,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,52</t>
+          <t>0,0; 10,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 6,9</t>
+          <t>1,63; 7,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 8,48</t>
+          <t>2,94; 8,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,92; 10,84</t>
+          <t>2,78; 9,99</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,53; 8,89</t>
+          <t>2,2; 8,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,21</t>
+          <t>0,42; 4,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 7,16</t>
+          <t>1,13; 7,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,44</t>
+          <t>0,0; 6,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 11,87</t>
+          <t>2,21; 12,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 9,79</t>
+          <t>1,09; 9,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 6,98</t>
+          <t>1,91; 6,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,57</t>
+          <t>1,25; 4,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 7,19</t>
+          <t>1,71; 6,49</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,36</t>
+          <t>0,0; 5,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 6,54</t>
+          <t>1,16; 6,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 8,22</t>
+          <t>0,77; 8,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 20,86</t>
+          <t>2,27; 20,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 8,03</t>
+          <t>0,91; 8,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,38; 12,57</t>
+          <t>1,4; 12,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 6,52</t>
+          <t>1,17; 6,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,57</t>
+          <t>1,46; 5,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 7,94</t>
+          <t>1,65; 7,41</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 6,93</t>
+          <t>1,45; 6,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 7,83</t>
+          <t>1,87; 8,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,47; 11,15</t>
+          <t>3,61; 11,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,07; 11,45</t>
+          <t>2,08; 11,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 9,37</t>
+          <t>0,84; 9,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,59; 11,79</t>
+          <t>2,64; 12,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,13; 6,69</t>
+          <t>2,04; 6,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 7,06</t>
+          <t>2,07; 6,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,03; 9,66</t>
+          <t>3,85; 9,73</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,72</t>
+          <t>2,09; 4,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,54; 5,32</t>
+          <t>2,63; 5,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,39; 7,18</t>
+          <t>3,42; 7,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,77; 8,7</t>
+          <t>2,81; 8,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,43</t>
+          <t>1,87; 5,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,74; 7,42</t>
+          <t>2,92; 7,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,65; 5,02</t>
+          <t>2,61; 5,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,74</t>
+          <t>2,64; 4,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,51; 6,36</t>
+          <t>3,63; 6,53</t>
         </is>
       </c>
     </row>
@@ -1417,22 +1417,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>962; 8210</t>
+          <t>971; 8388</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7757; 21139</t>
+          <t>7694; 22041</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4216; 18022</t>
+          <t>4140; 17200</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>848; 6849</t>
+          <t>867; 7397</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1442,22 +1442,22 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5123</t>
+          <t>0; 5473</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2062; 11780</t>
+          <t>2778; 12416</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6914; 22123</t>
+          <t>7659; 22669</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5021; 18654</t>
+          <t>4789; 17186</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4733; 16603</t>
+          <t>4103; 16693</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1035; 7971</t>
+          <t>1044; 10117</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2024; 12688</t>
+          <t>1997; 12675</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5723</t>
+          <t>0; 4663</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1992; 11670</t>
+          <t>2174; 12314</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>920; 8448</t>
+          <t>937; 8584</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5034; 18419</t>
+          <t>5044; 17350</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4269; 15846</t>
+          <t>4321; 17330</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4804; 18959</t>
+          <t>4510; 17101</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 7205</t>
+          <t>0; 7230</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1967; 11268</t>
+          <t>2001; 10826</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1062; 10977</t>
+          <t>1035; 11029</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>922; 8279</t>
+          <t>900; 8048</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>960; 8281</t>
+          <t>942; 8750</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1027; 9369</t>
+          <t>1045; 9271</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1946; 11343</t>
+          <t>2043; 11924</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3960; 15339</t>
+          <t>4029; 14760</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4076; 16518</t>
+          <t>3428; 15425</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2563; 12061</t>
+          <t>2518; 11757</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3825; 16149</t>
+          <t>3853; 17242</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6126; 19683</t>
+          <t>6372; 20614</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1925; 10629</t>
+          <t>1929; 10877</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>949; 10592</t>
+          <t>953; 10510</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3132; 14276</t>
+          <t>3195; 14844</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5695; 17837</t>
+          <t>5433; 18059</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6715; 22552</t>
+          <t>6597; 22303</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11981; 28742</t>
+          <t>11459; 28966</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12841; 29474</t>
+          <t>13057; 30053</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20728; 43390</t>
+          <t>21455; 43465</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20534; 43484</t>
+          <t>20699; 42437</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6940; 21806</t>
+          <t>7051; 20533</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6521; 20973</t>
+          <t>7246; 23098</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9209; 24915</t>
+          <t>9792; 25595</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23224; 43983</t>
+          <t>22869; 44669</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>30736; 57019</t>
+          <t>31715; 59310</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>33082; 59840</t>
+          <t>34159; 61460</t>
         </is>
       </c>
     </row>
